--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -17918,12 +17918,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -17948,12 +17948,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -17996,42 +17996,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18063,12 +18063,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -18141,40 +18141,185 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW121" t="inlineStr">
+      <c r="AW122" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
+      <c r="AX122" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY121" t="inlineStr">
+      <c r="AY122" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
+      <c r="AZ122" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA121" t="inlineStr">
+      <c r="BA122" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB121" t="inlineStr">
+      <c r="BB122" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC121" t="inlineStr">
+      <c r="BC122" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -18296,7 +18441,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -18306,7 +18451,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -17193,12 +17193,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17232,13 +17232,16 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>128</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>0.009059291080881595</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -17271,42 +17274,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -17338,12 +17341,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17368,7 +17371,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -17416,42 +17419,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17513,7 +17516,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -17658,7 +17661,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -17803,7 +17806,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -17948,7 +17951,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -18063,12 +18066,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -18093,12 +18096,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -18141,42 +18144,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18208,12 +18211,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -18286,40 +18289,185 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW122" t="inlineStr">
+      <c r="AW123" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY122" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA122" t="inlineStr">
+      <c r="BA123" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB122" t="inlineStr">
+      <c r="BB123" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC122" t="inlineStr">
+      <c r="BC123" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -18441,7 +18589,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
@@ -18451,7 +18599,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -18503,7 +18651,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>181</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16">
@@ -18513,7 +18661,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -18473,6 +18473,151 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18506,7 +18651,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18734,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -18599,7 +18744,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -17341,12 +17341,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17419,42 +17419,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17486,12 +17486,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -17564,42 +17564,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -18211,12 +18211,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -18241,12 +18241,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N122" t="n">
@@ -18289,42 +18289,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -18356,12 +18356,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -18434,42 +18434,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18501,12 +18501,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -18579,40 +18579,330 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW124" t="inlineStr">
+      <c r="AW125" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
+      <c r="AX125" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY124" t="inlineStr">
+      <c r="AY125" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ124" t="inlineStr">
+      <c r="AZ125" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA124" t="inlineStr">
+      <c r="BA125" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB124" t="inlineStr">
+      <c r="BB125" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC124" t="inlineStr">
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -18651,7 +18941,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18734,7 +19024,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -18744,7 +19034,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -29773,6 +29773,296 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
+      <c r="AT184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29806,7 +30096,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -29889,7 +30179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -29899,7 +30189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2084,6 +2129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2614,6 +2664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2759,6 +2814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2907,6 +2967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3203,6 +3268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3499,6 +3569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3795,6 +3870,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4091,6 +4171,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4239,6 +4324,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4384,6 +4474,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4529,6 +4624,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4674,6 +4774,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4819,6 +4924,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4964,6 +5074,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5109,6 +5224,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5254,6 +5374,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5399,6 +5524,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5547,6 +5677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6077,6 +6212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6222,6 +6362,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6518,6 +6663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6814,6 +6964,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7110,6 +7265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7406,6 +7566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7554,6 +7719,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7699,6 +7869,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7844,6 +8019,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7989,6 +8169,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8134,6 +8319,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8279,6 +8469,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8424,6 +8619,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8569,6 +8769,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8714,6 +8919,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8862,6 +9072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9007,6 +9222,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9152,6 +9372,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9448,6 +9673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9744,6 +9974,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10040,6 +10275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10336,6 +10576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10481,6 +10726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10626,6 +10876,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10771,6 +11026,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10916,6 +11176,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11061,6 +11326,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11206,6 +11476,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11351,6 +11626,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11496,6 +11776,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11641,6 +11926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11789,6 +12079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11934,6 +12229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12079,6 +12379,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12375,6 +12680,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12671,6 +12981,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12967,6 +13282,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13263,6 +13583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13408,6 +13733,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13553,6 +13883,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13698,6 +14033,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13843,6 +14183,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13988,6 +14333,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14133,6 +14483,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14278,6 +14633,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14423,6 +14783,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14568,6 +14933,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14716,6 +15086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15636,6 +16011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15781,6 +16161,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16077,6 +16462,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16373,6 +16763,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16669,6 +17064,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16965,6 +17365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17261,6 +17666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17406,6 +17816,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17551,6 +17966,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17696,6 +18116,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17841,6 +18266,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17986,6 +18416,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18131,6 +18566,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18276,6 +18716,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18421,6 +18866,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18566,6 +19016,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18714,6 +19169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21964,6 +22424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22109,6 +22574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22399,6 +22869,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22689,6 +23164,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22979,6 +23459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23269,6 +23754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23414,6 +23904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23559,6 +24054,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23704,6 +24204,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23849,6 +24354,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23994,6 +24504,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24139,6 +24654,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24284,6 +24804,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24429,6 +24954,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24574,6 +25104,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24722,6 +25257,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28362,6 +28902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28507,6 +29052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28797,6 +29347,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29087,6 +29642,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29377,6 +29937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29667,6 +30232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29957,6 +30527,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30102,6 +30677,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30247,6 +30827,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30392,6 +30977,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30537,6 +31127,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30682,6 +31277,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30827,6 +31427,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30972,6 +31577,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31117,6 +31727,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31265,6 +31880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34130,6 +34750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34275,6 +34900,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35145,6 +35775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35290,6 +35925,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35435,6 +36075,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35580,6 +36225,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35725,6 +36375,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35870,6 +36525,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36015,6 +36675,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36160,6 +36825,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36305,6 +36975,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36450,6 +37125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37173,6 +37853,11 @@
       <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">

--- a/diseases/d023/2026-2029.xlsx
+++ b/diseases/d023/2026-2029.xlsx
@@ -37925,6 +37925,151 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>anthrax</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
+      <c r="AT234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37958,7 +38103,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -38041,7 +38186,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -38051,7 +38196,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
